--- a/public/Participation_Importing_Template.xlsx
+++ b/public/Participation_Importing_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED15E10-9180-4B1B-9391-30FD9D36F97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC6A802-196F-4D59-9155-DE03551409B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="15661" windowHeight="9848" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Participation" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Date From</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>Distribution Place</t>
-  </si>
-  <si>
-    <t>Distribution Date</t>
   </si>
   <si>
     <t>Gender</t>
@@ -106,7 +103,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -116,12 +113,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -153,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -169,7 +160,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="4"/>
@@ -494,11 +484,10 @@
     <col min="5" max="7" width="10.86328125" style="5" customWidth="1"/>
     <col min="8" max="9" width="23.06640625" style="5" customWidth="1"/>
     <col min="10" max="10" width="22.33203125" style="5" customWidth="1"/>
-    <col min="11" max="11" width="21.59765625" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="9.06640625" style="6"/>
+    <col min="11" max="16384" width="9.06640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -524,13 +513,10 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/public/Participation_Importing_Template.xlsx
+++ b/public/Participation_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC6A802-196F-4D59-9155-DE03551409B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D73A0D8-2036-4075-ADDB-3482B1C26C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -520,6 +520,22 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid unit." sqref="A2:A1048576" xr:uid="{16959CB0-58A0-4244-BEFB-F734BB6C4584}">
+      <formula1>"AGRISTAT, AMIA, DRRM"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted date is out of the coverage." sqref="D2:D1048576 E2:E1048576" xr:uid="{21F376D6-A72D-4A18-A825-61ECF07B6BEE}">
+      <formula1>46023</formula1>
+      <formula2>46752</formula2>
+    </dataValidation>
+    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted time is out of the coverage." sqref="F2:F1048576 G2:G1048576" xr:uid="{62CD2D36-5C16-45F8-837F-3AB9B8CC1F22}">
+      <formula1>0.208333333333333</formula1>
+      <formula2>0.833333333333333</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid input." sqref="I2:I1048576" xr:uid="{A99A9BAA-70B8-4F83-8F59-040C12EB8BD2}">
+      <formula1>"Male, Female"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/public/Participation_Importing_Template.xlsx
+++ b/public/Participation_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D73A0D8-2036-4075-ADDB-3482B1C26C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2760B48-652B-4E24-BAA2-CC8A31C447A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Date From</t>
   </si>
@@ -55,12 +55,6 @@
   </si>
   <si>
     <t>Unit</t>
-  </si>
-  <si>
-    <t>Time Start</t>
-  </si>
-  <si>
-    <t>Time End</t>
   </si>
   <si>
     <t>Distribution Place</t>
@@ -474,20 +468,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="4"/>
     <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
     <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
     <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
-    <col min="5" max="7" width="10.86328125" style="5" customWidth="1"/>
-    <col min="8" max="9" width="23.06640625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="22.33203125" style="5" customWidth="1"/>
-    <col min="11" max="16384" width="9.06640625" style="6"/>
+    <col min="5" max="5" width="10.86328125" style="5" customWidth="1"/>
+    <col min="6" max="7" width="23.06640625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -503,24 +497,18 @@
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid unit." sqref="A2:A1048576" xr:uid="{16959CB0-58A0-4244-BEFB-F734BB6C4584}">
       <formula1>"AGRISTAT, AMIA, DRRM"</formula1>
     </dataValidation>
@@ -528,11 +516,7 @@
       <formula1>46023</formula1>
       <formula2>46752</formula2>
     </dataValidation>
-    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted time is out of the coverage." sqref="F2:F1048576 G2:G1048576" xr:uid="{62CD2D36-5C16-45F8-837F-3AB9B8CC1F22}">
-      <formula1>0.208333333333333</formula1>
-      <formula2>0.833333333333333</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid input." sqref="I2:I1048576" xr:uid="{A99A9BAA-70B8-4F83-8F59-040C12EB8BD2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid input." sqref="G2:G1048576" xr:uid="{A99A9BAA-70B8-4F83-8F59-040C12EB8BD2}">
       <formula1>"Male, Female"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/Participation_Importing_Template.xlsx
+++ b/public/Participation_Importing_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2760B48-652B-4E24-BAA2-CC8A31C447A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1687F7C-8BA5-4D1B-8048-9AB8300C66FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -54,13 +54,13 @@
     <t>Destination</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
     <t>Distribution Place</t>
   </si>
   <si>
     <t>Gender</t>
+  </si>
+  <si>
+    <t>Assignment</t>
   </si>
 </sst>
 </file>
@@ -471,7 +471,7 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="4"/>
+    <col min="1" max="1" width="12.265625" style="4" customWidth="1"/>
     <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
     <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
     <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
@@ -483,7 +483,7 @@
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -501,10 +501,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/public/Participation_Importing_Template.xlsx
+++ b/public/Participation_Importing_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1687F7C-8BA5-4D1B-8048-9AB8300C66FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6C1C91-9505-4B8C-97EF-619DFD0958FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -60,7 +60,7 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>Assignment</t>
+    <t>Certificate Template From</t>
   </si>
 </sst>
 </file>
@@ -97,7 +97,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -107,6 +107,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -138,13 +150,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -153,6 +163,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,18 +493,17 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.265625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" style="5" customWidth="1"/>
-    <col min="6" max="7" width="23.06640625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="6"/>
+    <col min="1" max="1" width="35.59765625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="35.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="23.06640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -491,19 +512,19 @@
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>5</v>
       </c>
     </row>

--- a/public/Participation_Importing_Template.xlsx
+++ b/public/Participation_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6C1C91-9505-4B8C-97EF-619DFD0958FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3CF421-6A15-46EF-BC57-08A2DAA3046C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -155,15 +155,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -175,6 +166,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -493,17 +493,17 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.59765625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="35.59765625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" style="3" customWidth="1"/>
-    <col min="6" max="7" width="23.06640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="4"/>
+    <col min="1" max="1" width="35.59765625" style="6" customWidth="1"/>
+    <col min="2" max="3" width="35.59765625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" style="7" customWidth="1"/>
+    <col min="6" max="7" width="23.06640625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="7" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" s="3" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -518,13 +518,13 @@
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
